--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0095.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0095.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Core Package</t>
+          <t>Gói Lõi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Rover Appearance Switch assets</t>
+          <t>Tài Nguyên Chuyển Đổi Ngoại Hình Rover</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[Storyline] Regional Storyline Assets</t>
+          <t>Tài nguyên Cốt truyện Khu vực</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[Môi trường] Jinzhou và các khu vực khác</t>
+          <t>[Môi trường] Khu vực Jinzhou và các vùng lân cận</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[Environment] Tethys' Deep</t>
+          <t>Tổ Tacet Tethys' Deep</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Cốt truyện] Tài nguyên cốt truyện ở Ragunna và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Ragunna và Các Khu Vực Khác</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Môi trường] Ragunna và các khu vực khác</t>
+          <t>[Môi trường] Khu vực Ragunna và các vùng lân cận</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Môi trường] Septimont và các khu vực khác</t>
+          <t>[Môi trường] Khu vực Septimont và các vùng lân cận</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Cốt truyện] Tài nguyên cốt truyện ở Septimont và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Septimont và Các Khu Vực Khác</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Storyline] Lahai-Roi Storyline Assets</t>
+          <t>Tài Nguyên Cốt Truyện Lahai-Roi</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Region] [Region] Lahai-Roi</t>
+          <t>Lahai-Roi</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Cốt truyện] Tài nguyên cốt truyện ở Roya Frostlands và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Vùng Đất Băng Giá Roya và Các Khu Vực Khác</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Region] Roya Frostlands</t>
+          <t>Vùng Đất Băng Giá Roya</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>[Cốt truyện] Tài nguyên cốt truyện ở Dimmr Plains và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Đồng Bằng Dimmr và Các Khu Vực Khác</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>[Region] Dimmr Plains</t>
+          <t>Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Rinascita và các khu vực khác</t>
+          <t>Khu vực Rinascita và các vùng khác</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Roya Frostlands và các khu vực khác</t>
+          <t>Vùng Đất Băng Giá Roya và các khu vực khác</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Con mắt Khai phá</t>
+          <t>Con Mắt Giải Khai</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Zhao Lingze</t>
+          <t>Triệu Lăng Trạch</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Leader Looi</t>
+          <t>Đội trưởng Looi</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Divine Hearing</t>
+          <t>Thính Giác Thần Thánh</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Old-Style Scissors</t>
+          <t>Kéo Cắt Kiểu Cũ</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Red Hair Ribbon</t>
+          <t>Nơ Tóc Màu Đỏ</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Protective Charm</t>
+          <t>Bùa Hộ Mệnh</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tinted Sunglasses</t>
+          <t>Kính Râm Nhuộm Màu</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Casket of Fate</t>
+          <t>Quan Tài Định Mệnh</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Noise-Cancelling Headset</t>
+          <t>Tai Nghe Khử Tiếng Ồn</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Mùa hè Khởi đầu Câu chuyện</t>
+          <t>Mùa Hè Nơi Câu Chuyện Bắt Đầu</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>The Long Rainy Season</t>
+          <t>Mùa Mưa Dài</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Blurred Features</t>
+          <t>Nét Mờ Ảo</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ác mộng Tháng Hai</t>
+          <t>Ác Mộng Tháng Hai</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Vượt qua Hết mùa Hè</t>
+          <t>Vượt Qua Ngày Hạ Tàn</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Người Tuần tra và Đạo sĩ</t>
+          <t>Tuần Tra Viên và Đạo Sĩ</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Đạo của Sự Linh Hoạt</t>
+          <t>Đạo Uốn Dẻo</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Đồng Môn Khác Phái</t>
+          <t>Những Đồng Môn Khác Phái</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Earthly Immortal, Heavenly Sheep</t>
+          <t>Thần Tiên Hạ Giới, Cừu Trên Trời</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Crimson Rainfall</t>
+          <t>Mưa Đỏ Rơi</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>"Quái Vật" Trên Tàu</t>
+          <t>"Quái vật" trên Tàu</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hành Trình Trở Về</t>
+          <t>Con đường trở về</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Bữa Tiệc Khai Mạc và Những Điều Ước</t>
+          <t>Tiệc Khai Mạc và Lời Nguyện Ước</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Fate</t>
+          <t>Định Mệnh</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Goodbye, Farewell</t>
+          <t>Tạm biệt, vĩnh biệt.</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Human Heart</t>
+          <t>Trái Tim Con Người</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Parting</t>
+          <t>Chia Tay</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>"Happy Birthday"</t>
+          <t>"Chúc mừng sinh nhật"</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Bình Minh Đọng Lại Trên Vùng Đất Hoang</t>
+          <t>Bình Minh Trì Trệ trên Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Ánh Sao Lấp Lánh Trong Mống Mắt</t>
+          <t>Ánh Sao Chảy Trong Mống Mắt</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Chronorift Metropolis Chương II: Bình Minh Đọng Lại Trên Vùng Đất Hoang</t>
+          <t>Đô Thị Dị Thời Gian Chương II: Bình Minh Đọng Lại Trên Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Chronorift Metropolis Chương II: Ánh Sao Lấp Lánh Trong Mống Mắt</t>
+          <t>Đô Thị Dị Thời Gian Chương II: Ánh Sao Lấp Lánh Trong Mống Mắt</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Trauma Disruption</t>
+          <t>Giải Trừ Sang Chấn</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Critical Disruption</t>
+          <t>Phá Bạo Kích</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Strike Disruption</t>
+          <t>Phá vỡ đòn đánh!</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Cacopohony Disruption</t>
+          <t>Sự Gián Đoạn Hỗn Âm</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Storm Disruption</t>
+          <t>Gián Đoạn Bão Tố</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Surge Disruption</t>
+          <t>Gián Đoạn Dòng Năng Lượng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Transmission Disruption</t>
+          <t>Giao Tiếp Bị Gián Đoạn</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Focus Disruption</t>
+          <t>Gián Đoạn Tập Trung</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Blackhole Disruption</t>
+          <t>Sự Phá Vỡ Hố Đen</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Vortex Disruption</t>
+          <t>Sự Gián Đoạn Xoáy Lốc</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Flash Disruption</t>
+          <t>Gián Đoạn Tia Chớp</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Incineration Disruption</t>
+          <t>Gián Đoạn Thiêu Rụi</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Echo Disruption</t>
+          <t>Sự Gián Đoạn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Symphonic Disruption</t>
+          <t>Sự Phá Vỡ Giao Hưởng</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Ascending Disruption</t>
+          <t>Sự Phá Vỡ Thăng Hoa</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Đạt 1.100 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.100 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Đạt 1.300 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.300 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Đạt 2.300 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.300 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Heart Radio Channel</t>
+          <t>Kênh Phát Thanh Trái Tim</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Playlist</t>
+          <t>Danh sách phát</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Favorites</t>
+          <t>Yêu thích</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Reorder</t>
+          <t>Sắp Xếp Lại</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Đã bật Lặp lại</t>
+          <t>Chế độ lặp đã kích hoạt</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đã bật Phát ngẫu nhiên</t>
+          <t>Đã bật chế độ xáo trộn</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Đã bật Thứ tự mặc định</t>
+          <t>Chế độ Mặc định đã kích hoạt</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Favorites Limit Reached</t>
+          <t>Đã đạt giới hạn yêu thích</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Không Favorite Songs</t>
+          <t>Chưa có bài hát yêu thích nào.</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Bạn có bài hát mới</t>
+          <t>Ngươi có bài hát mới</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Adaptive Hook</t>
+          <t>Móc Câu Thích Ứng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Mô-đun Hỗ trợ</t>
+          <t>Mô-đun Hỗ Trợ</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Motorbike (Auto Parking)</t>
+          <t>Xe máy (Tự động đỗ)</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Motorbike Appearance</t>
+          <t>Giao Diện Xe Máy</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Customization</t>
+          <t>Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Livery</t>
+          <t>Họa tiết</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Import Preset</t>
+          <t>Nhập Cài Đặt Sẵn</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Đang sử dụng</t>
+          <t>Đang Sử Dụng</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Preset Applied</t>
+          <t>Đã Áp Dụng Cài Đặt Sẵn</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Không More Presets</t>
+          <t>Không Còn Khuôn Mẫu</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Premium Livery</t>
+          <t>Bộ Vỏ Cao Cấp</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Custom Livery</t>
+          <t>Màu Sơn Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Basic Livery</t>
+          <t>Mẫu Sơn Cơ Bản</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Basic Livery</t>
+          <t>Mẫu Sơn Cơ Bản</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Polmes Rhombus x2</t>
+          <t>Khối Polmes Hình thoi x2</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Polmes Rhombus x4</t>
+          <t>Khối Polmes Hình thoi x4</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Polmes Rhombus x6</t>
+          <t>Khối Polmes Hình thoi x6</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Namipon Rhombus x2</t>
+          <t>Hình thoi Namipon x2</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Namipon Rhombus x4</t>
+          <t>Hình thoi Namipon x4</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Namipon Circle x2</t>
+          <t>Vòng Tròn Namipon x2</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Sweet Tooth Namipon Circle x2</t>
+          <t>Vòng Namipon Háu Ăn Ngọt x2</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Sweet Tooth Namipon Circle x4</t>
+          <t>Vòng Namipon Háu Ăn Ngọt x4</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Sweet Tooth Namipon Circle x6</t>
+          <t>Vòng Namipon Háu Ăn Ngọt x6</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Namipon Courier Rhombus x2</t>
+          <t>Hình Thoi Namipon Đặc Nhiệm x2</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Namipon Courier Rhombus x4</t>
+          <t>Hình Thoi Namipon Đặc Nhiệm x4</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Namipon Courier Hexagon x2</t>
+          <t>Lục Giác Namipon Đặc Nhiệm x2</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Sales Champ Rhombus x2</t>
+          <t>Hình Thoi Quán Quân x2</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Sales Champ Hexagon x2</t>
+          <t>Hình Lục Giác Quán Quân x2</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Sales Champ Hexagon x4</t>
+          <t>Hình Lục Giác Quán Quân x4</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Yakuza Namipon Hexagon x2</t>
+          <t>Yakuza Namipon Lục Giác x2</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Yakuza Namipon Hexagon x4</t>
+          <t>Yakuza Namipon Lục Giác x4</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Bowtie Butler Hexagon x2</t>
+          <t>Hầu Cận Nơ Bướm Hình Lục Giác x2</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Bowtie Butler Circle x2</t>
+          <t>Hội Quản Gia Nơ Bướm x2</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Bowtie Butler Rhombus x2</t>
+          <t>Hầu Cận Nơ Bướm Hình Thoi x2</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Platform Guardian Circle x2</t>
+          <t>Vòng Bảo Vệ Nền Tảng x2</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Platform Guardian Circle x4</t>
+          <t>Vòng Bảo Vệ Nền Tảng x4</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Platform Guardian Hexagon x2</t>
+          <t>Hình Lục Giác Bảo Vệ Nền Tảng x2</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Vacationer Namipon Circle x2</t>
+          <t>Vòng tròn Du khách Namipon x2</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Vacationer Namipon Circle x4</t>
+          <t>Vòng tròn Du khách Namipon x4</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Vacationer Namipon Circle x2</t>
+          <t>Vòng tròn Du khách Namipon x2</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Regional Lối chơi</t>
+          <t>Hệ thống chơi khu vực</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Regional Feature</t>
+          <t>Đặc trưng khu vực</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Weather Simulation</t>
+          <t>Mô Phỏng Thời Tiết</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Motorbike Specs</t>
+          <t>Thông Số Xe Máy</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Modding EXP</t>
+          <t>Kinh Nghiệm Nâng Cấp</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Cấp độ Modding</t>
+          <t>Cấp Độ Nâng Cấp</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Tốc Độ</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Boost Speed</t>
+          <t>Tốc độ Tăng cường</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Energy Tank</t>
+          <t>Bình Năng Lượng</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Energy Recovery Rate</t>
+          <t>Tốc Độ Phục Hồi Năng Lượng</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Shield Strength</t>
+          <t>Sức Mạnh Khiên</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Expansion Mô-đun Installed</t>
+          <t>Đã cài đặt Mô-đun Mở rộng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện</t>
+          <t>Chưa đáp ứng điều kiện</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Expansion Mô-đun Installed</t>
+          <t>Đã cài đặt Mô-đun Mở rộng</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Current Expansion Modules</t>
+          <t>Mô-đun Mở Rộng Hiện Tại</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Mô-đun Effect Overview</t>
+          <t>Tổng quan Hiệu ứng Mô-đun</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn ghim</t>
+          <t>Đã đạt giới hạn đánh dấu</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Unpinned</t>
+          <t>Thoát Khỏi Xiềng Xích</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Decisive Victory</t>
+          <t>Chiến thắng quyết định</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Narrow Victory</t>
+          <t>Chiến Thắng Sít Sao</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Suggested Deck 1</t>
+          <t>Bộ bài đề xuất 1</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Suggested Deck 2</t>
+          <t>Bộ bài đề xuất 2</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Suggested Deck 3</t>
+          <t>Bộ bài đề xuất 3</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Quay về Cockpit</t>
+          <t>Quay về buồng lái</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tiêu hao khi kết thúc vòng đấu</t>
+          <t>Được tiêu thụ vào cuối lượt.</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Duelist Search</t>
+          <t>Tìm Kiếm Đấu Sĩ</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Phần thưởng lần đầu thắng</t>
+          <t>Phần Thưởng Chiến Thắng Đầu Tiên</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Phần thưởng thắng</t>
+          <t>Phần thưởng Chiến thắng</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ sự kiện "Peaks of Prestige: Rekindled Duel" để mở khóa</t>
+          <t>Hoàn thành Sự Kiện "Đỉnh Danh Vọng: Cuộc Đọ Sức Nảy Lửa" để mở khóa</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Nightmare: Gulpuff</t>
+          <t>Ác Mộng: Gulpuff</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Frostscourge Stalker</t>
+          <t>Kẻ Rình Rập Băng Giá</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Calcified Junrock</t>
+          <t>Đá Junrock Hóa Thạch</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Frostbite Coleoid</t>
+          <t>Mực Băng Giá Coleoid</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Abyssal Gladius</t>
+          <t>Kiếm Vực Sâu</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Broken Bell</t>
+          <t>Chuông Vỡ</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Shepherd's Tent</t>
+          <t>Lều Người Chăn Cừu</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ice Chrysalis</t>
+          <t>Kén băng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Snowfall Realm</t>
+          <t>Vùng Đất Tuyết Rơi</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Explosive Charge</t>
+          <t>Bom nổ</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Suppressive Fire</t>
+          <t>Hỏa Lực Áp Chế</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Sư Tử Vinh Quang</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Diệt Vong Vinh Quang</t>
+          <t>Tàn Tích Vinh Quang</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Origin Chamber</t>
+          <t>Điện Nguồn Cội</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Hooscamp Clapperclaw</t>
+          <t>Quái Hooscamp Ném Đá</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Hurriclaw</t>
+          <t>Vuốt Bão Cuồng</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Nightmare: Feilian Beringal</t>
+          <t>Ác Mộng: Feilian Beringal</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Bamboo Grove</t>
+          <t>Rừng Tre</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Geospider S4</t>
+          <t>Nhện Địa Chấn S4</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Twin Nova: Nebulous Cannon</t>
+          <t>Song Tinh: Đại Bác Vụ Nổ</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Inverted Tower</t>
+          <t>Tháp Đảo Ngược</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Mining Drone</t>
+          <t>Drone Khai Thác</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Sabercat Prowler</t>
+          <t>Kẻ Rình Rập Mèo Đao</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Gladiator Gear</t>
+          <t>Trang Bị Đấu Sĩ</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Bàn Thờ Hòa Âm</t>
+          <t>Bệ Phối Khí</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tượng Crownless</t>
+          <t>Tượng Vô Vương</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>KU-Roro: Max Firepower</t>
+          <t>KU-Roro: Hỏa Lực Tối Đa</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>KU-Roro: Impregnable Wall</t>
+          <t>KU-Roro: Bức Tường Bất Diệt</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Lava Larva</t>
+          <t>Ấu trùng dung nham</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Waystone</t>
+          <t>Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Reserve Weapons</t>
+          <t>Vũ khí dự phòng</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Hologram Map</t>
+          <t>Bản Đồ Hologram</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Transport Unit XE-01</t>
+          <t>Đơn Vị Vận Chuyển XE-01</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Glacio</t>
+          <t>Vực Sâu Chìm: Glacio</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Glacio</t>
+          <t>Tàn Dư Lửa Cháy: Glacio</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Glacio</t>
+          <t>Vùng Đất Chết: Glacio</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đỉnh Vinh Dự</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
